--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-12.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-12.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583991070009</v>
+        <v>5583988212779</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Jocsiã</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jose Galdino de Souza Filho</t>
+          <t>Jocsiã dos Santos Moreira</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583987112154</v>
+        <v>5583988295029</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brendon</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brendon Luna Santos</t>
+          <t>Maria Jose Alves de Andrade</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583994113889</v>
+        <v>5583993930086</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Italo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wesley Vinicius Cavalcante Pereira</t>
+          <t>Italo Ramos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583988150307</v>
+        <v>5583986243983</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Germana</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Germana de Almeida da Silva Bezerra</t>
+          <t>Antonio Valdevino de Melo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583988714190</v>
+        <v>5583986688094</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lusiane</t>
+          <t>Robeciano</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lusiane Silva do Rego Araujo</t>
+          <t>Robeciano Luiz da Silva</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583999354233</v>
+        <v>5583987668630</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Marcilio</t>
+          <t>Adenilza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marcilio Joaquim de Oliveira</t>
+          <t>Adenilza Marinho Silva</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583988998531</v>
+        <v>5583991070009</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Maria Jose Martiliano de Oliveira</t>
+          <t>Jose Galdino de Souza Filho</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583996222463</v>
+        <v>5583987112154</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Brendon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paula Raylyny Nascimento Lins</t>
+          <t>Brendon Luna Santos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583988307720</v>
+        <v>5583994113889</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rosenildo</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rosenildo Rodrigues de Queiroz</t>
+          <t>Wesley Vinicius Cavalcante Pereira</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583988432969</v>
+        <v>5583988150307</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gilson</t>
+          <t>Germana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gilson Jose Geronimo</t>
+          <t>Germana de Almeida da Silva Bezerra</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583988809740</v>
+        <v>5583988714190</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rosinaldo</t>
+          <t>Lusiane</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rosinaldo da Silva Matias</t>
+          <t>Lusiane Silva do Rego Araujo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583987536186</v>
+        <v>5583999354233</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Esrom</t>
+          <t>Marcilio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Esrom Feitosa</t>
+          <t>Marcilio Joaquim de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583986895383</v>
+        <v>5583988998531</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Francisco Menezes de Souza</t>
+          <t>Maria Jose Martiliano de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583999775390</v>
+        <v>5583996222463</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paulo Andre da Silva</t>
+          <t>Paula Raylyny Nascimento Lins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583988213825</v>
+        <v>5583988307720</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karla</t>
+          <t>Rosenildo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Karla Emenuella Barbosa</t>
+          <t>Rosenildo Rodrigues de Queiroz</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583987181789</v>
+        <v>5583988432969</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marinalva</t>
+          <t>Gilson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marinalva de Oliveira Bezerra</t>
+          <t>Gilson Jose Geronimo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583998407552</v>
+        <v>5583988511364</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Casc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Francisco Leurimar da Silva</t>
+          <t>Casc Pb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583986204143</v>
+        <v>5583988809740</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jaqueline</t>
+          <t>Rosinaldo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa Ribeiro</t>
+          <t>Rosinaldo da Silva Matias</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583991178529</v>
+        <v>5583987536186</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Francineide</t>
+          <t>Esrom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Francineide Campos Padilha</t>
+          <t>Esrom Feitosa</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583993374154</v>
+        <v>5583986895383</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Marcia</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marcia Regina da Silva</t>
+          <t>Francisco Menezes de Souza</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583987946489</v>
+        <v>5583999775390</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jennifer Marinho do Nascimento Fernandes</t>
+          <t>Paulo Andre da Silva</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583996074134</v>
+        <v>5583988213825</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Karla</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Anderson Rodrigo Brito</t>
+          <t>Karla Emenuella Barbosa</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5581994047051</v>
+        <v>5583987181789</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Marinalva</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jose Romero Silva Laurentino</t>
+          <t>Marinalva de Oliveira Bezerra</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583991999247</v>
+        <v>5583998407552</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Efigenio</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Efigenio Jose da Silva</t>
+          <t>Francisco Leurimar da Silva</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583987677117</v>
+        <v>5583986204143</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jaqueline</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Maria Eduarda Rodrigues</t>
+          <t>Jaqueline Sousa Ribeiro</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583987468338</v>
+        <v>5583991178529</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kariny</t>
+          <t>Francineide</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kariny Santana Alves</t>
+          <t>Francineide Campos Padilha</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583986332009</v>
+        <v>5583993374154</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Robson</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Robson Rosendo de Santana</t>
+          <t>Marcia Regina da Silva</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583998307895</v>
+        <v>5583987946489</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Larissa Teixeira da Silva</t>
+          <t>Jennifer Marinho do Nascimento Fernandes</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583982002556</v>
+        <v>5583996074134</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ana Priscilla Lima</t>
+          <t>Anderson Rodrigo Brito</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583981228620</v>
+        <v>5581994047051</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Samuel Luna Barbosa da Silva</t>
+          <t>Jose Romero Silva Laurentino</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583996101074</v>
+        <v>5583991999247</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Efigenio</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eduardo Roberto Oliva</t>
+          <t>Efigenio Jose da Silva</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5561981291767</v>
+        <v>5583987677117</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Andreia</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Andreia Francini</t>
+          <t>Maria Eduarda Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583998415865</v>
+        <v>5583987468338</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Saul</t>
+          <t>Kariny</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saul Regis Lima Alves</t>
+          <t>Kariny Santana Alves</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583999928313</v>
+        <v>5583986332009</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edmir</t>
+          <t>Robson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Edmir Jose Junior</t>
+          <t>Robson Rosendo de Santana</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583988682247</v>
+        <v>5583998307895</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luis Antonio Fernandes Sousa</t>
+          <t>Larissa Teixeira da Silva</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583986561328</v>
+        <v>5583982002556</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leone</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Leone da Silva Gomes</t>
+          <t>Ana Priscilla Lima</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583991617735</v>
+        <v>5583981228620</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bernadete</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bernadete Cabral de Melo</t>
+          <t>Samuel Luna Barbosa da Silva</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5511981810884</v>
+        <v>5583996101074</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fabio Souza dos Santos</t>
+          <t>Eduardo Roberto Oliva</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583988047170</v>
+        <v>5561981291767</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Andreia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vera Lucia Paz Barreto Borges</t>
+          <t>Andreia Francini</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583988117606</v>
+        <v>5583988722799</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Matheus</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Matheus Fernandes dos Santos</t>
+          <t>S T Manutencoes</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583987065321</v>
+        <v>5583998415865</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Saul</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Marcos da Silva</t>
+          <t>Saul Regis Lima Alves</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583991721957</v>
+        <v>5583999928313</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Edmir</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Roberto Vieira Batista</t>
+          <t>Edmir Jose Junior</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583921459700</v>
+        <v>5583988682247</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Waldir</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Waldir Martins de Araujo</t>
+          <t>Luis Antonio Fernandes Sousa</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988958236</v>
+        <v>5583986561328</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Claudemir</t>
+          <t>Leone</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Claudemir Neves Pereira</t>
+          <t>Leone da Silva Gomes</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583998567176</v>
+        <v>5583991617735</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Bernadete</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Residencial Multifamiliar Isabelly Mirante</t>
+          <t>Bernadete Cabral de Melo</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583991091106</v>
+        <v>5511981810884</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jose Fernandes da Silva</t>
+          <t>Fabio Souza dos Santos</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583987767134</v>
+        <v>5583988047170</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Joao Batista Fontes</t>
+          <t>Vera Lucia Paz Barreto Borges</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583991982825</v>
+        <v>5583988117606</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Marciel</t>
+          <t>Matheus</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marciel Ancelmo de Farias</t>
+          <t>Matheus Fernandes dos Santos</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583996300669</v>
+        <v>5583987065321</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Laercio</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Laercio de Melo Machado</t>
+          <t>Marcos da Silva</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583988716802</v>
+        <v>5583991721957</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jose Bezerra Leite Neto</t>
+          <t>Roberto Vieira Batista</t>
         </is>
       </c>
     </row>
